--- a/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
+++ b/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E67658B-0923-477C-ACCA-96FD2395BC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38CB848-525C-4781-AD88-CA7AFDE308A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="4" r:id="rId2"/>
-    <sheet name="ASM1" sheetId="3" r:id="rId3"/>
+    <sheet name="Week 3" sheetId="5" r:id="rId3"/>
+    <sheet name="ASM1" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>STT</t>
   </si>
@@ -104,17 +105,54 @@
 Trải nghiệm người dùng: Việc tập trung vào "Cảnh báo sự kiện" thay vì "Thông báo thủ công" đảm bảo người dùng chỉ nhận được thông tin khi thực sự cần hành động, giúp họ quản trị chuỗi cung ứng theo cơ chế "quản lý theo ngoại lệ" (Management by exception).
 Lợi thế cạnh tranh: Các tính năng mới tập trung vào việc giảm lãng phí (thông qua dự báo nhu cầu) và giảm chi phí vận hành (thông qua gom đơn), đây là hai yếu tố sống còn quyết định sự thành công của một nền tảng chuỗi cung ứng thực phẩm tươi.</t>
   </si>
+  <si>
+    <t>Doubt (Nghi ngờ/Đặt vấn đề)</t>
+  </si>
+  <si>
+    <t>"Dự án FreshConnect của tôi sử dụng NestJS làm Backend chính và Python FastAPI cho các tác vụ AI (Forecasting, Route Optimization). Tôi lo ngại về việc đảm bảo tính toàn vẹn dữ liệu và độ trễ khi truyền các tập dữ liệu lớn về lịch sử đơn hàng từ PostgreSQL qua FastAPI để huấn luyện mô hình Prophet. Hãy phân tích các rủi ro về hiệu suất và đề xuất cách tối ưu hóa việc giao tiếp giữa hai dịch vụ này trong môi trường Docker."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI phân tích rằng việc gửi JSON lớn qua REST API có thể gây trễ. AI đề xuất sử dụng Redis làm hàng đợi (Message Queue) với BullMQ  hoặc chia sẻ Database ở mức độ đọc (Read-only access) cho dịch vụ AI.
+Quyết định: Nhóm quyết định sử dụng Redis làm Cache trung gian để đồng bộ dữ liệu nhanh và xây dựng các REST API tối giản chỉ gửi các tham số cần thiết, thay vì gửi toàn bộ lịch sử đơn hàng mỗi lần gọi.</t>
+  </si>
+  <si>
+    <t>Teach (Giảng dạy/Xây dựng nội dung)</t>
+  </si>
+  <si>
+    <t>"Dựa trên danh sách Actors gồm Restaurant Manager, Supplier, Logistics Dispatcher và AI Optimization Engine , hãy xây dựng một kịch bản chi tiết (User Scenario) cho chức năng 'Tối ưu hóa lộ trình giao hàng'. Kịch bản phải thể hiện rõ sự tương tác giữa Logistics Dispatcher, Google Maps API và AI Engine từ lúc gom đơn đến khi Driver nhận nhiệm vụ."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phản hồi của AI: AI tạo ra bảng mô tả trình tự: (1) Dispatcher chọn danh sách đơn hàng -&gt; (2) AI Engine tính toán lộ trình dựa trên vị trí và tải trọng xe -&gt; (3) Hệ thống gọi Google Maps API để lấy ETA thực tế -&gt; (4) Driver nhận thông báo qua App.
+Quyết định: Nhóm thống nhất sơ đồ tuần tự (Sequence Diagram) này và quyết định sẽ ưu tiên tích hợp Google OR-Tools vào dịch vụ Python để xử lý thuật toán tối ưu hóa lộ trình.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Correct (Chỉnh sửa/Hoàn thiện)</t>
+  </si>
+  <si>
+    <t>"Nhóm tôi chuyên về Node.js nhưng đang cân nhắc giữa việc dùng TypeORM hay Prisma cho dự án FreshConnect. Với yêu cầu về một hệ thống có nhiều quan hệ phức tạp giữa đơn hàng, kho hàng và lịch trình logistics , hãy so sánh và đưa ra lựa chọn tốt nhất để tối ưu hóa thời gian phát triển trong phạm vi một học kỳ."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phản hồi của AI: AI so sánh Prisma (dễ học, tự động sinh type-safe, trực quan cho quan hệ phức tạp) và TypeORM (truyền thống, linh hoạt hơn với Query Builder). AI khuyên dùng Prisma để đẩy nhanh tiến độ MVP.
+Quyết định: Nhóm quyết định chọn Prisma ORM kết hợp với PostgreSQL để đảm bảo tính nhất quán dữ liệu và giúp việc phát triển các tính năng như 'Theo dõi tồn kho' và 'Gợi ý nhà cung cấp' trở nên nhanh chóng, ít lỗi hơn. </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -151,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -162,23 +200,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -555,7 +599,7 @@
       <c r="B3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -568,6 +612,77 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE059D6-C78C-4518-A06A-5E141951E9CE}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="37.21875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+    <col min="4" max="4" width="47.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
+++ b/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\SWP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38CB848-525C-4781-AD88-CA7AFDE308A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5075FF62-AD74-4908-ABDB-6A0C9B8D3B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="4" r:id="rId2"/>
     <sheet name="Week 3" sheetId="5" r:id="rId3"/>
-    <sheet name="ASM1" sheetId="3" r:id="rId4"/>
+    <sheet name="Week 4" sheetId="6" r:id="rId4"/>
+    <sheet name="ASM1" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
   <si>
     <t>STT</t>
   </si>
@@ -135,17 +136,64 @@
     <t xml:space="preserve">Phản hồi của AI: AI so sánh Prisma (dễ học, tự động sinh type-safe, trực quan cho quan hệ phức tạp) và TypeORM (truyền thống, linh hoạt hơn với Query Builder). AI khuyên dùng Prisma để đẩy nhanh tiến độ MVP.
 Quyết định: Nhóm quyết định chọn Prisma ORM kết hợp với PostgreSQL để đảm bảo tính nhất quán dữ liệu và giúp việc phát triển các tính năng như 'Theo dõi tồn kho' và 'Gợi ý nhà cung cấp' trở nên nhanh chóng, ít lỗi hơn. </t>
   </si>
+  <si>
+    <t>Connect (Kết nối &amp; Tích hợp hệ thống)</t>
+  </si>
+  <si>
+    <t>"Dự án FreshConnect cần tích hợp toàn diện giữa Backend NestJS, dịch vụ AI FastAPI, và Database PostgreSQL. Hãy hướng dẫn cách cấu hình kết nối tối ưu, xử lý pooling database và viết một script test integration tự động để đảm bảo luồng dữ liệu từ lúc User đặt đơn hàng, hệ thống gọi AI tối ưu lộ trình, đến khi lưu kết quả vào DB không bị nghẽn."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI đề xuất kiến trúc kết nối thông qua Prisma client trong NestJS với cấu hình connection_limit phù hợp cho PostgreSQL. Cung cấp cấu trúc mã nguồn cho Integration Test sử dụng Jest và Supertest để giả lập luồng dữ liệu end-to-end, đồng thời gợi ý cơ chế retry-mechanism khi gọi API sang FastAPI nếu gặp sự cố mạng.
+Quyết định: Nhóm thống nhất áp dụng cấu hình Connection Pooling tối ưu cho DB. Triển khai bộ kiểm thử tích hợp (Integration Test) tự động chạy trước mỗi đợt gộp code (Merge Request) nhằm kiểm soát chặt chẽ tính toàn vẹn dữ liệu giữa các dịch vụ.</t>
+  </si>
+  <si>
+    <t>Test &amp; Validate (Kiểm thử &amp; Đánh giá hiệu năng)</t>
+  </si>
+  <si>
+    <t>"Chúng tôi lo ngại về thời gian phản hồi của thuật toán tối ưu lộ trình (OR-Tools trên FastAPI) khi số lượng đơn hàng tăng lên đột biến (từ 100 đến 1000 đơn). Hãy gợi ý cách viết script đo tải (Load Testing) bằng Locust hoặc Artillery và các giải pháp bộ nhớ đệm (Caching) nâng cao để giảm tải cho AI Engine."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI hướng dẫn cài đặt Locust để giả lập hàng trăm request đồng thời vào API FastAPI. AI đề xuất chiến lược Caching: lưu trữ các lộ trình phổ biến hoặc các cụm khoảng cách cố định vào Redis với thời gian hết hạn (TTL) hợp lý, tránh việc AI phải tính toán lại các bài toán trùng lặp.
+Quyết định: Nhóm quyết định sử dụng Locust để thực hiện bài test hiệu năng. Thống nhất tích hợp Redis Cache cho các truy vấn khoảng cách lặp đi lặp lại từ Google Maps API và kết quả định tuyến của AI để giảm chi phí API và hạ tải cho CPU.</t>
+  </si>
+  <si>
+    <t>Deploy (Triển khai &amp; Tối ưu hóa đóng gói)</t>
+  </si>
+  <si>
+    <t>"Hãy xây dựng file Dockerfile tối ưu (Multi-stage build) cho cả dự án NestJS và FastAPI để giảm dung lượng image khi deploy. Đồng thời, thiết lập một pipeline CI/CD cơ bản bằng GitHub Actions để tự động build và deploy lên môi trường Staging mỗi khi có commit mới trên nhánh main."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI cung cấp cấu trúc file Dockerfile Multi-stage giúp giảm size image NestJS từ ~1GB xuống còn dưới 200MB và FastAPI xuống còn ~300MB. Cung cấp file YAML cấu hình GitHub Actions hoàn chỉnh bao gồm các bước: Lint, Test, Build Docker Image, và SSH deploy lên VPS staging.
+Quyết định: Nhóm áp dụng hoàn toàn cấu hình Multi-stage build để tối ưu tài nguyên lưu trữ và tăng tốc độ deploy. Triển khai thành công pipeline CI/CD qua GitHub Actions, giúp tự động hóa 100% quy trình cập nhật sản phẩm, giảm thiểu lỗi cấu hình thủ công.</t>
+  </si>
+  <si>
+    <t>Secure &amp; Monitor (Bảo mật &amp; Giám sát vận hành)</t>
+  </si>
+  <si>
+    <t>"Làm thế nào để bảo vệ các API endpoints của dịch vụ AI FastAPI khỏi việc bị truy cập trái phép và quản lý các biến môi trường (JWT secret, API keys) an toàn? Ngoài ra, hãy gợi ý một giải pháp log tập trung gọn nhẹ để theo dõi lỗi hệ thống khi vận hành."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI đề xuất sử dụng API Key kết hợp với Middleware xác thực nội bộ (Internal Token Auth) giữa NestJS và FastAPI. Khuyến nghị dùng thư viện Winston (NestJS) và Loguru (FastAPI) để chuẩn hóa định dạng log (JSON format), và sử dụng Docker-compose để chạy một container Promtail/Loki/Grafana gọn nhẹ để gom log.
+Quyết định: Nhóm quyết định thiết lập cơ chế xác thực Token nội bộ giữa hai dịch vụ để cô lập hoàn toàn AI Engine với môi trường bên ngoài. Sử dụng GitHub Secrets để truyền biến môi trường khi deploy và cài đặt hệ thống giám sát lỗi cơ bản qua log file để kịp thời xử lý sự cố.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -189,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -200,23 +248,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -663,7 +717,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -683,6 +737,90 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5C778F-E897-444F-8693-62D09D5A0A0D}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="46.77734375" customWidth="1"/>
+    <col min="3" max="3" width="31.21875" customWidth="1"/>
+    <col min="4" max="4" width="46.6640625" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="229.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
+++ b/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
@@ -5,26 +5,27 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\SWP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\SWP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5075FF62-AD74-4908-ABDB-6A0C9B8D3B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E84BC5-B511-453B-A325-27884D2F3165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="4" r:id="rId2"/>
     <sheet name="Week 3" sheetId="5" r:id="rId3"/>
     <sheet name="Week 4" sheetId="6" r:id="rId4"/>
-    <sheet name="ASM1" sheetId="3" r:id="rId5"/>
+    <sheet name="Week 5" sheetId="7" r:id="rId5"/>
+    <sheet name="ASM1" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
   <si>
     <t>STT</t>
   </si>
@@ -176,17 +177,80 @@
     <t>Phản hồi của AI: AI đề xuất sử dụng API Key kết hợp với Middleware xác thực nội bộ (Internal Token Auth) giữa NestJS và FastAPI. Khuyến nghị dùng thư viện Winston (NestJS) và Loguru (FastAPI) để chuẩn hóa định dạng log (JSON format), và sử dụng Docker-compose để chạy một container Promtail/Loki/Grafana gọn nhẹ để gom log.
 Quyết định: Nhóm quyết định thiết lập cơ chế xác thực Token nội bộ giữa hai dịch vụ để cô lập hoàn toàn AI Engine với môi trường bên ngoài. Sử dụng GitHub Secrets để truyền biến môi trường khi deploy và cài đặt hệ thống giám sát lỗi cơ bản qua log file để kịp thời xử lý sự cố.</t>
   </si>
+  <si>
+    <t>Optimize (Tối ưu hóa thuật toán OR-Tools)</t>
+  </si>
+  <si>
+    <t>"Thuật toán tối ưu lộ trình bằng OR-Tools trên FastAPI hiện tại tốn nhiều thời gian khi số lượng điểm giao hàng lên tới 500 điểm. Hãy hướng dẫn cách cấu hình Parallel Search, thiết lập thời gian giới hạn (Time Limit) và thêm ràng buộc về khung giờ giao hàng (Time Windows) để tối ưu hiệu năng."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI hướng dẫn cấu hình RoutingSearchParameters để giới hạn thời gian tìm kiếm dưới 30 giây và tối ưu hóa bộ nhớ. Sử dụng AddDimension để xử lý Time Windows một cách hiệu quả, tránh quá tải CPU khi xử lý ma trận khoảng cách lớn.
+Quyết định: Nhóm thống nhất cấu hình Parallel Search và giới hạn thời gian tìm kiếm tối đa là 20 giây để cân bằng giữa tốc độ phản hồi hệ thống và độ tối ưu của lộ trình giao hàng.</t>
+  </si>
+  <si>
+    <t>Real-time (Đồng bộ vị trí thời gian thực qua WebSockets)</t>
+  </si>
+  <si>
+    <t>"Chúng tôi muốn làm tính năng theo dõi vị trí tài xế theo thời gian thực trên bản đồ Admin. Hãy hướng dẫn cách xây dựng WebSocket Gateway bằng NestJS kết hợp với Redis Pub/Sub để phát (broadcast) tọa độ GPS từ app tài xế đến trang quản trị một cách mượt mà."</t>
+  </si>
+  <si>
+    <t>Analytics (Xây dựng Dashboard và Tối ưu truy vấn dữ liệu lớn)</t>
+  </si>
+  <si>
+    <t>"Hãy gợi ý cách thiết kế cơ sở dữ liệu và viết các truy vấn tổng hợp hiệu quả để phục vụ cho Dashboard của Admin, bao gồm các chỉ số: tổng quãng đường đã đi, tỷ lệ giao hàng đúng giờ (SLA), và doanh thu theo từng vùng miền mà không làm chậm DB."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI cung cấp giải pháp tạo các Materialized Views trong PostgreSQL để lưu trữ dữ liệu tổng hợp sẵn, giúp Dashboard tải nhanh mà không cần quét lại toàn bộ bảng lịch sử đơn hàng lớn mỗi khi User truy cập.
+Quyết định: Nhóm thống nhất áp dụng Materialized Views và thiết lập một cron job chạy vào cuối ngày để làm mới dữ liệu, đảm bảo Dashboard hiển thị trực quan, mượt mà và không gây nghẽn DB.</t>
+  </si>
+  <si>
+    <t>Security (Bảo mật và Phân quyền hệ thống)</t>
+  </si>
+  <si>
+    <t>"Làm thế nào để bảo vệ các API endpoints của dịch vụ AI FastAPI khỏi việc bị truy cập trái phép từ bên ngoài và quản lý các biến môi trường (JWT secret, API keys) an toàn khi phân quyền giữa các vai trò Admin, Dispatcher, Driver?"</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI đề xuất cơ chế xác thực Token nội bộ (Internal API Key Auth) giữa NestJS và FastAPI, kết hợp Guards trong NestJS để phân quyền chi tiết (RBAC). Khuyến nghị dùng GitHub Secrets để quản lý biến môi trường.
+Quyết định: Nhóm triển khai API Key bảo mật cho cổng giao tiếp giữa hai dịch vụ và áp dụng nghiêm ngặt cơ chế RBAC cho toàn bộ hệ thống API Endpoints.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Stress Test (Kiểm thử tải và Đánh giá độ chịu tải hệ thống)</t>
+  </si>
+  <si>
+    <t>"Hãy hướng dẫn cách viết script đo tải (Load Testing) bằng Locust để kiểm tra khả năng chịu tải của hệ thống khi có 2000 request đồng thời vào các API tạo đơn hàng và tối ưu lộ trình."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI hướng dẫn cấu hình Locust script mô phỏng hành vi của Driver và Dispatcher, đồng thời chỉ ra các điểm nghẽn (bottlenecks) tiềm ẩn ở tầng kết nối Database khi tải cao.
+Quyết định: Nhóm tiến hành chạy load test, phát hiện lỗi nghẽn kết nối và quyết định tăng kích thước Connection Pool của Prisma lên gấp đôi để xử lý mượt mà lượng truy cập lớn.</t>
+  </si>
+  <si>
+    <t>Handover (Kiểm thử chấp nhận UAT &amp; Hoàn thiện tài liệu bàn giao)</t>
+  </si>
+  <si>
+    <t>"Dự án đã đi đến giai đoạn cuối. Hãy hướng dẫn cách viết tài liệu kỹ thuật (Technical Documentation) chuẩn chỉnh cho toàn bộ hệ thống FreshConnect và thiết lập kịch bản kiểm thử chấp nhận người dùng (UAT)."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI cung cấp template tài liệu kỹ thuật chi tiết bằng Markdown, hướng dẫn sử dụng Swagger/OpenAPI để tự động hóa tài liệu API và gợi ý các kịch bản kiểm thử UAT cho từng vai trò người dùng.
+Quyết định: Nhóm hoàn thiện tài liệu hệ thống, đóng gói mã nguồn, tiến hành chạy thử nghiệm UAT nội bộ thành công và chuẩn bị sẵn sàng bàn giao sản phẩm.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -237,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -248,23 +312,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -554,14 +624,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.77734375" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" customWidth="1"/>
-    <col min="4" max="4" width="72.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" customWidth="1"/>
+    <col min="4" max="4" width="72.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -575,7 +645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -589,7 +659,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="250.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="242.25" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -611,14 +681,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.77734375" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" customWidth="1"/>
-    <col min="4" max="4" width="72.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" customWidth="1"/>
+    <col min="4" max="4" width="72.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -646,7 +716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -668,14 +738,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE059D6-C78C-4518-A06A-5E141951E9CE}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.21875" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" customWidth="1"/>
-    <col min="4" max="4" width="47.109375" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" customWidth="1"/>
+    <col min="4" max="4" width="47.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -689,7 +759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="240" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -703,7 +773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="195" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -717,7 +787,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -739,15 +809,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5C778F-E897-444F-8693-62D09D5A0A0D}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="46.77734375" customWidth="1"/>
-    <col min="3" max="3" width="31.21875" customWidth="1"/>
-    <col min="4" max="4" width="46.6640625" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" customWidth="1"/>
+    <col min="2" max="2" width="46.7109375" customWidth="1"/>
+    <col min="3" max="3" width="31.28515625" customWidth="1"/>
+    <col min="4" max="4" width="46.7109375" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -761,7 +831,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="229.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="229.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -775,7 +845,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="210" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -789,7 +859,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="240" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -803,7 +873,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="255" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="12" t="s">
         <v>34</v>
@@ -821,9 +891,122 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854D79C7-6BFD-4291-81B6-EE8BA46EF5FC}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="62.5703125" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="4" max="4" width="72.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
+++ b/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\SWP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E84BC5-B511-453B-A325-27884D2F3165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C1B0B9-D8FC-4A12-9308-4F65823731E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23136" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,15 @@
     <sheet name="Week 3" sheetId="5" r:id="rId3"/>
     <sheet name="Week 4" sheetId="6" r:id="rId4"/>
     <sheet name="Week 5" sheetId="7" r:id="rId5"/>
-    <sheet name="ASM1" sheetId="3" r:id="rId6"/>
+    <sheet name="Week 6" sheetId="8" r:id="rId6"/>
+    <sheet name="ASM1" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <t>STT</t>
   </si>
@@ -233,17 +234,84 @@
     <t>Phản hồi của AI: AI cung cấp template tài liệu kỹ thuật chi tiết bằng Markdown, hướng dẫn sử dụng Swagger/OpenAPI để tự động hóa tài liệu API và gợi ý các kịch bản kiểm thử UAT cho từng vai trò người dùng.
 Quyết định: Nhóm hoàn thiện tài liệu hệ thống, đóng gói mã nguồn, tiến hành chạy thử nghiệm UAT nội bộ thành công và chuẩn bị sẵn sàng bàn giao sản phẩm.</t>
   </si>
+  <si>
+    <t>Production (Triển khai môi trường thực tế)</t>
+  </si>
+  <si>
+    <t>"Để chuẩn bị đưa ứng dụng vào thực tế, hãy hướng dẫn cách triển khai toàn bộ hệ thống lên môi trường Production an toàn, đảm bảo tính sẵn sàng cao (High Availability) để hệ thống luôn hoạt động ổn định khi lượng lớn khách hàng truy cập mua sắm."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI đề xuất kiến trúc sử dụng Load Balancer, tách biệt hoàn toàn Database Server và Application Server. Khuyến nghị cấu hình Nginx làm Reverse Proxy và thiết lập chứng chỉ SSL/TLS (Let's Encrypt) cho các domain.
+Quyết định: Nhóm quyết định deploy lên cụm VPS với Nginx, cấu hình HTTPS bắt buộc và thiết lập tường lửa (UFW) chỉ mở các port cần thiết để tối đa hóa bảo mật.</t>
+  </si>
+  <si>
+    <t>Payment (Tích hợp cổng thanh toán &amp; Quản lý dòng tiền)</t>
+  </si>
+  <si>
+    <t>"Mục tiêu cốt lõi của dự án là giúp bà con quản lý được dòng tiền minh bạch. Hãy hướng dẫn cách tích hợp cổng thanh toán trực tuyến (như VNPay hoặc MoMo) vào NestJS một cách an toàn và thiết kế luồng đối soát tự động hàng ngày."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI hướng dẫn tạo API xử lý Webhook từ cổng thanh toán, bắt buộc xác thực chữ ký (Signature Hash) để chống giả mạo. Gợi ý sử dụng Transaction trong PostgreSQL để đảm bảo không xảy ra lỗi double-spending.
+Quyết định: Nhóm quyết định tích hợp VNPay, triển khai luồng Webhook bảo mật và xây dựng một cron-job đối soát doanh thu tự động vào 23h59 mỗi ngày.</t>
+  </si>
+  <si>
+    <t>Marketing &amp; SEO (Tối ưu hóa công cụ tìm kiếm)</t>
+  </si>
+  <si>
+    <t>"Chúng tôi cần tối ưu hóa công cụ tìm kiếm (SEO) và hiệu suất tải trang cho giao diện người dùng (Frontend) nhằm mục đích quảng bá hiệu quả các sản phẩm đặc sản của từng vùng miền. Hãy gợi ý các kỹ thuật Server-Side Rendering (SSR) hoặc Static Site Generation (SSG)."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI phân tích ưu điểm của Next.js (SSR/SSG) trong việc tạo thẻ Meta động (Open Graph) cho từng sản phẩm và đề xuất dùng Redis để cache các trang HTML tĩnh nhằm giảm TTFB (Time to First Byte).
+Quyết định: Nhóm áp dụng Next.js cho giao diện người tiêu dùng, tối ưu hóa các thẻ SEO cho từng mặt hàng nông sản và cấu hình Redis cache để trang web tải dưới 1 giây.</t>
+  </si>
+  <si>
+    <t>Monitoring (Giám sát và Cảnh báo sự cố)</t>
+  </si>
+  <si>
+    <t>"Sau khi go-live, làm sao để theo dõi sức khỏe của hệ thống (Uptime, Memory Usage) và nhận cảnh báo (Alert) tự động qua Telegram/Slack nếu API quản lý đơn hàng hoặc dịch vụ AI FastAPI bị sập?"</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI đề xuất cài đặt Prometheus để thu thập metrics và Grafana để trực quan hóa dữ liệu. Hướng dẫn thiết lập Alertmanager để tự động bắn thông báo Webhook qua Telegram khi CPU/RAM vượt ngưỡng 80% hoặc có lỗi 5xx.
+Quyết định: Nhóm tích hợp thành công Prometheus &amp; Grafana, đồng thời tạo một bot Telegram dành riêng cho đội phát triển để nhận cảnh báo sự cố tức thời 24/7.</t>
+  </si>
+  <si>
+    <t>Disaster Recovery (Sao lưu và Phục hồi dữ liệu)</t>
+  </si>
+  <si>
+    <t>"Hãy xây dựng chiến lược sao lưu dữ liệu (Backup Strategy) tự động cho cơ sở dữ liệu PostgreSQL để phòng ngừa rủi ro mất mát thông tin giao dịch, lịch sử định tuyến và dữ liệu người dùng."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI cung cấp shell script sử dụng pg_dump chạy định kỳ qua Cron job, thực hiện nén file (gzip) và tự động đồng bộ (sync) file backup lên cloud storage (AWS S3 hoặc Google Drive).
+Quyết định: Nhóm thiết lập lịch sao lưu cơ sở dữ liệu 2 lần/ngày và lưu trữ trên một Server dự phòng độc lập để đảm bảo khả năng phục hồi dữ liệu trong vòng 15 phút nếu có sự cố.</t>
+  </si>
+  <si>
+    <t>Review (Tổng kết &amp; Bảo vệ dự án)</t>
+  </si>
+  <si>
+    <t>"Dự án đã hoàn tất triển khai. Hãy hỗ trợ xây dựng cấu trúc bài thuyết trình tổng kết (Pitch Deck) nhấn mạnh vào giá trị kinh doanh, kiến trúc kỹ thuật nổi bật (AI Routing, Microservices) và những khó khăn đã giải quyết."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI đưa ra dàn ý 10 slide chuẩn, tập trung làm nổi bật bài toán tối ưu chi phí logistics, hệ thống quản lý tài chính minh bạch cho nhà cung cấp và sự ổn định của hệ thống dưới tải trọng lớn.
+Quyết định: Nhóm sử dụng dàn ý này để chốt slide bảo vệ dự án, tự tin trình bày giải pháp kỹ thuật và demo trực tiếp các tính năng core trên môi trường Production.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -301,7 +369,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -312,23 +380,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1004,6 +1078,119 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE75B42-A07E-44EA-A1C6-EF0F79346583}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="55.140625" customWidth="1"/>
+    <col min="3" max="3" width="37.5703125" customWidth="1"/>
+    <col min="4" max="4" width="53.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
+++ b/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\SWP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C1B0B9-D8FC-4A12-9308-4F65823731E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6C18FB-8B17-405F-8EF0-E462673D11A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23136" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,15 @@
     <sheet name="Week 4" sheetId="6" r:id="rId4"/>
     <sheet name="Week 5" sheetId="7" r:id="rId5"/>
     <sheet name="Week 6" sheetId="8" r:id="rId6"/>
-    <sheet name="ASM1" sheetId="3" r:id="rId7"/>
+    <sheet name="Week 7" sheetId="9" r:id="rId7"/>
+    <sheet name="ASM1" sheetId="3" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="90">
   <si>
     <t>STT</t>
   </si>
@@ -294,17 +295,84 @@
     <t>Phản hồi của AI: AI đưa ra dàn ý 10 slide chuẩn, tập trung làm nổi bật bài toán tối ưu chi phí logistics, hệ thống quản lý tài chính minh bạch cho nhà cung cấp và sự ổn định của hệ thống dưới tải trọng lớn.
 Quyết định: Nhóm sử dụng dàn ý này để chốt slide bảo vệ dự án, tự tin trình bày giải pháp kỹ thuật và demo trực tiếp các tính năng core trên môi trường Production.</t>
   </si>
+  <si>
+    <t>Feedback &amp; Maintenance (Bảo trì &amp; Xử lý lỗi sau Go-live)</t>
+  </si>
+  <si>
+    <t>"Hệ thống đã chạy thực tế. Hãy hướng dẫn cách thiết lập kênh thu thập phản hồi người dùng (User Feedback) tự động và quy trình triage (phân loại) bug để xử lý các lỗi phát sinh trong tuần đầu ra mắt."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI đề xuất tích hợp Sentry để bắt lỗi Frontend tự động và sử dụng Jira/Trello API để tạo ticket mỗi khi có lỗi hoặc feedback từ form liên hệ.
+Quyết định: Nhóm tích hợp Sentry và xây dựng form góp ý cho ứng dụng Nông Sản Việt, kết nối thẳng về bot Telegram để hỗ trợ bà con nhanh chóng kịp thời.</t>
+  </si>
+  <si>
+    <t>AI Forecasting (Dự báo nhu cầu nông sản)</t>
+  </si>
+  <si>
+    <t>"Để giúp nhà cung cấp chuẩn bị nguồn hàng tốt hơn, hãy gợi ý cách huấn luyện một mô hình AI chuỗi thời gian (Time-Series Forecasting) cơ bản để dự báo nhu cầu các mặt hàng đặc sản theo mùa vụ."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI đề xuất sử dụng Prophet hoặc LSTM trên Python để phân tích dữ liệu lịch sử đặt hàng, kết hợp với các biến số về thời tiết và ngày lễ.
+Quyết định: Nhóm quyết định thu thập thêm dữ liệu thực tế và bắt đầu xây dựng mô hình Prophet trên FastAPI, cung cấp biểu đồ dự báo xu hướng ngay trong Dashboard quản trị.</t>
+  </si>
+  <si>
+    <t>Mobile App Integration (Mở rộng hệ sinh thái Mobile)</t>
+  </si>
+  <si>
+    <t>"Dự án dự định phát triển thêm app cho tài xế và khách hàng. Hãy hướng dẫn cách cấu hình lại API Gateway và cập nhật tài liệu Swagger để đội Mobile có thể dễ dàng tích hợp."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI hướng dẫn tách biệt các version API (v1, v2), tối ưu hóa payload trả về cho Mobile (giảm dung lượng JSON) và cung cấp Postman Collection cập nhật.
+Quyết định: Nhóm tiến hành versioning toàn bộ API, tạo các endpoint chuyên biệt, nhẹ gọn hơn để tối ưu băng thông cho thiết bị di động.</t>
+  </si>
+  <si>
+    <t>Loyalty Program (Chương trình khách hàng thân thiết)</t>
+  </si>
+  <si>
+    <t>"Chúng tôi muốn tăng tỷ lệ giữ chân khách hàng. Hãy gợi ý cấu trúc cơ sở dữ liệu để quản lý điểm thưởng (Reward Points) và hệ thống mã giảm giá (Voucher/Coupon) cho người dùng mua nhiều."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI cung cấp schema cho bảng LoyaltyPoints và Vouchers, hướng dẫn xử lý concurrency (race condition) khi nhiều người cùng áp dụng một mã giảm giá giới hạn số lượng.
+Quyết định: Nhóm cập nhật DB schema, áp dụng cơ chế khóa lạc quan (Optimistic Locking) trong Prisma để xử lý mã giảm giá một cách an toàn và chính xác.</t>
+  </si>
+  <si>
+    <t>Data Warehouse (Lưu trữ và phân tích dữ liệu dài hạn)</t>
+  </si>
+  <si>
+    <t>"Dữ liệu giao dịch ngày càng phình to. Hãy hướng dẫn cách thiết lập một luồng ETL (Extract, Transform, Load) cơ bản để chuyển dữ liệu cũ từ PostgreSQL sang một database phụ phục vụ cho báo cáo BI sau này."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI đề xuất sử dụng cron-job để extract dữ liệu định kỳ và thiết lập một database PostgreSQL chuyên đọc (Read-Replica/OLAP).
+Quyết định: Nhóm chọn giải pháp thiết lập Read-Replica cho PostgreSQL để giảm tải cho database chính, đáp ứng nhu cầu truy xuất báo cáo dòng tiền phức tạp mà không làm chậm hệ thống.</t>
+  </si>
+  <si>
+    <t>Roadmap (Lập kế hoạch phát triển Phase 2)</t>
+  </si>
+  <si>
+    <t>"Tuần đầu go-live đã thành công. Hãy giúp chúng tôi phác thảo lộ trình phát triển (Roadmap) cho 3 tháng tiếp theo, tập trung vào việc mở rộng quy mô hợp tác với các nhà vườn và hợp tác xã lớn hơn."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: AI gợi ý roadmap 3 tháng bao gồm: Tối ưu UI/UX, tích hợp eKYC xác thực danh tính cho nhà cung cấp, và chuyển đổi dần sang kiến trúc Event-Driven (RabbitMQ) để chịu tải cao hơn.
+Quyết định: Nhóm chốt Roadmap Phase 2, lên danh sách các tính năng ưu tiên và chuẩn bị tài liệu để trình bày hướng mở rộng quy mô dự án.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -369,7 +437,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -380,23 +448,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1088,10 +1162,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -1115,7 +1189,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1191,6 +1265,120 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B94F58A-D036-43DF-B29B-7261E51DD160}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" customWidth="1"/>
+    <col min="4" max="4" width="53.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
+++ b/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\SWP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6C18FB-8B17-405F-8EF0-E462673D11A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30141AD9-7D4D-451B-A8F0-B3B579E9AF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,15 @@
     <sheet name="Week 5" sheetId="7" r:id="rId5"/>
     <sheet name="Week 6" sheetId="8" r:id="rId6"/>
     <sheet name="Week 7" sheetId="9" r:id="rId7"/>
-    <sheet name="ASM1" sheetId="3" r:id="rId8"/>
+    <sheet name="Week 8" sheetId="10" r:id="rId8"/>
+    <sheet name="ASM1" sheetId="3" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="108">
   <si>
     <t>STT</t>
   </si>
@@ -355,17 +356,84 @@
     <t>Phản hồi của AI: AI gợi ý roadmap 3 tháng bao gồm: Tối ưu UI/UX, tích hợp eKYC xác thực danh tính cho nhà cung cấp, và chuyển đổi dần sang kiến trúc Event-Driven (RabbitMQ) để chịu tải cao hơn.
 Quyết định: Nhóm chốt Roadmap Phase 2, lên danh sách các tính năng ưu tiên và chuẩn bị tài liệu để trình bày hướng mở rộng quy mô dự án.</t>
   </si>
+  <si>
+    <t>Architecture (Kiến trúc Event-Driven cho đơn hàng)</t>
+  </si>
+  <si>
+    <t>"Dự án không dùng IoT nữa mà tập trung vào khả năng chịu tải khi có các đợt Flash Sale nông sản. Hãy thiết lập RabbitMQ làm Message Queue để xử lý hàng ngàn yêu cầu đặt hàng cùng lúc mà không làm sập Database."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Đề xuất kiến trúc dùng RabbitMQ để nhận đơn hàng (Producer) đưa vào Queue, sau đó các Worker Service (Consumer) sẽ từ từ xử lý và insert vào PostgreSQL.
+Quyết định: Chuyển đổi luồng tạo đơn hàng sang bất đồng bộ qua RabbitMQ, đảm bảo hệ thống không bị nghẽn (bottleneck) vào giờ cao điểm.</t>
+  </si>
+  <si>
+    <t>Fintech (Báo cáo dòng tiền cho nhà cung cấp)</t>
+  </si>
+  <si>
+    <t>"Mục tiêu chính là giúp bà con nông dân quản lý dòng tiền. Hãy viết các truy vấn SQL nâng cao để thống kê doanh thu, công nợ và lợi nhuận theo từng hợp tác xã mỗi ngày."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Cung cấp các câu truy vấn sử dụng Window Functions và thiết lập cron-job trong NestJS để tự động chốt sổ, đối soát công nợ vào cuối ngày.
+Quyết định: Triển khai module báo cáo tài chính, cung cấp biểu đồ dòng tiền trực quan trên Dashboard của nhà cung cấp.</t>
+  </si>
+  <si>
+    <t>Notification (Thông báo trạng thái thời gian thực)</t>
+  </si>
+  <si>
+    <t>"Cần gửi thông báo ngay lập tức cho khách hàng và tài xế khi đơn hàng chuyển trạng thái (Đã xác nhận, Đang lấy hàng). Hãy tích hợp Firebase Cloud Messaging (FCM)."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Hướng dẫn sử dụng firebase-admin để quản lý Token của thiết bị và bắn Push Notification từ Backend NestJS.
+Quyết định: Tích hợp thành công FCM, đảm bảo các bên liên quan nhận được cập nhật trạng thái đơn hàng ngay lập tức trên điện thoại.</t>
+  </si>
+  <si>
+    <t>eKYC (Xác thực nhà cung cấp tự động)</t>
+  </si>
+  <si>
+    <t>"Để onboarding nhà vườn mới nhanh chóng, cần tự động trích xuất thông tin từ ảnh Căn cước hoặc Giấy phép kinh doanh. Hãy thiết lập luồng OCR (Optical Character Recognition)."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Đề xuất sử dụng Google Cloud Vision API để đọc text từ ảnh tải lên, kết hợp regex để bóc tách Tên, Mã số thuế và Địa chỉ.
+Quyết định: Áp dụng eKYC vào luồng đăng ký đối tác, giảm thiểu thời gian duyệt hồ sơ thủ công của Admin.</t>
+  </si>
+  <si>
+    <t>AI Routing (Định tuyến đa kho - Multi-Depot)</t>
+  </si>
+  <si>
+    <t>"Hệ thống đã mở rộng ra nhiều kho trung chuyển khác nhau. Hãy cập nhật mô hình OR-Tools để điều phối xe tải đi lấy hàng từ nhiều kho (Multi-Depot Vehicle Routing Problem)."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Hướng dẫn định nghĩa lại ma trận khoảng cách, thêm node cho các điểm kho và thiết lập điểm xuất phát/kết thúc động cho từng xe.
+Quyết định: Nâng cấp thành công thuật toán AI, tối ưu hóa được quãng đường xe chạy luân chuyển giữa các kho hàng và điểm giao.</t>
+  </si>
+  <si>
+    <t>Review (Kiểm thử Sprint chịu tải)</t>
+  </si>
+  <si>
+    <t>"Hãy tạo kịch bản kiểm thử cho Sprint này: Giả lập 500 người dùng cùng đặt mua một mặt hàng đặc sản (Flash Sale) để xem RabbitMQ và AI Routing hoạt động ra sao."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Cung cấp script Locust gửi API tạo đơn ồ ạt, kết hợp hướng dẫn xem log tiêu thụ message trên RabbitMQ Management UI.
+Quyết định: Chạy script load test, xác nhận hệ thống xử lý mượt mà luồng dữ liệu lớn, chốt tính năng Phase 2.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -437,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -448,23 +516,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -772,14 +846,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" customWidth="1"/>
-    <col min="4" max="4" width="72.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="36.88671875" customWidth="1"/>
+    <col min="4" max="4" width="72.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -793,7 +867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -807,7 +881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="242.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="250.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -829,14 +903,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" customWidth="1"/>
-    <col min="4" max="4" width="72.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="36.88671875" customWidth="1"/>
+    <col min="4" max="4" width="72.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -850,7 +924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -864,7 +938,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -886,14 +960,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE059D6-C78C-4518-A06A-5E141951E9CE}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" customWidth="1"/>
-    <col min="4" max="4" width="47.140625" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+    <col min="4" max="4" width="47.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -907,7 +981,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="240" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -921,7 +995,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="195" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -935,7 +1009,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -957,15 +1031,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5C778F-E897-444F-8693-62D09D5A0A0D}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="46.7109375" customWidth="1"/>
-    <col min="3" max="3" width="31.28515625" customWidth="1"/>
-    <col min="4" max="4" width="46.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.140625" customWidth="1"/>
+    <col min="2" max="2" width="46.6640625" customWidth="1"/>
+    <col min="3" max="3" width="31.33203125" customWidth="1"/>
+    <col min="4" max="4" width="46.6640625" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -979,7 +1053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="229.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="229.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -993,7 +1067,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="210" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1007,7 +1081,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="240" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1021,7 +1095,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="255" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="12" t="s">
         <v>34</v>
@@ -1041,14 +1115,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854D79C7-6BFD-4291-81B6-EE8BA46EF5FC}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="62.5703125" customWidth="1"/>
+    <col min="2" max="2" width="62.5546875" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
-    <col min="4" max="4" width="72.7109375" customWidth="1"/>
+    <col min="4" max="4" width="72.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1062,7 +1136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1076,7 +1150,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1090,7 +1164,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1104,7 +1178,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1118,7 +1192,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1132,7 +1206,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1154,14 +1228,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE75B42-A07E-44EA-A1C6-EF0F79346583}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="55.140625" customWidth="1"/>
-    <col min="3" max="3" width="37.5703125" customWidth="1"/>
-    <col min="4" max="4" width="53.28515625" customWidth="1"/>
+    <col min="2" max="2" width="55.109375" customWidth="1"/>
+    <col min="3" max="3" width="37.5546875" customWidth="1"/>
+    <col min="4" max="4" width="53.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1175,7 +1249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1189,7 +1263,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1203,7 +1277,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1217,7 +1291,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1231,7 +1305,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1245,7 +1319,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1267,15 +1341,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B94F58A-D036-43DF-B29B-7261E51DD160}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="56.140625" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" customWidth="1"/>
-    <col min="4" max="4" width="53.28515625" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="56.109375" customWidth="1"/>
+    <col min="3" max="3" width="35.6640625" customWidth="1"/>
+    <col min="4" max="4" width="53.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1289,7 +1363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1303,7 +1377,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1317,7 +1391,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1331,7 +1405,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1345,7 +1419,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1359,7 +1433,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1379,9 +1453,122 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F7923E-0FE5-4029-9481-11345A93CD30}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="51.33203125" customWidth="1"/>
+    <col min="3" max="3" width="32.88671875" customWidth="1"/>
+    <col min="4" max="4" width="37" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
+++ b/AI Audit log_TranDinhQuocNhat_DE190627.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\SWP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30141AD9-7D4D-451B-A8F0-B3B579E9AF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC1DD91-EE7F-46C5-A41E-B2B99417994F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -21,14 +21,16 @@
     <sheet name="Week 6" sheetId="8" r:id="rId6"/>
     <sheet name="Week 7" sheetId="9" r:id="rId7"/>
     <sheet name="Week 8" sheetId="10" r:id="rId8"/>
-    <sheet name="ASM1" sheetId="3" r:id="rId9"/>
+    <sheet name="Week9" sheetId="11" r:id="rId9"/>
+    <sheet name="Week10" sheetId="12" r:id="rId10"/>
+    <sheet name="ASM1" sheetId="3" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="144">
   <si>
     <t>STT</t>
   </si>
@@ -416,17 +418,144 @@
     <t>Phản hồi của AI: Cung cấp script Locust gửi API tạo đơn ồ ạt, kết hợp hướng dẫn xem log tiêu thụ message trên RabbitMQ Management UI.
 Quyết định: Chạy script load test, xác nhận hệ thống xử lý mượt mà luồng dữ liệu lớn, chốt tính năng Phase 2.</t>
   </si>
+  <si>
+    <t>Security (Bảo mật API tài chính)</t>
+  </si>
+  <si>
+    <t>"Hướng dẫn rà soát lỗ hổng bảo mật (Security Audit) cho các API liên quan đến quản lý dòng tiền và đối soát doanh thu của nhà cung cấp."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Đề xuất mã hóa dữ liệu nhạy cảm bằng AES-256, áp dụng Rate Limiting và kiểm tra lỗ hổng SQL Injection/XSS.
+Quyết định: Áp dụng bảo mật nhiều lớp, mã hóa các trường dữ liệu tài chính trong PostgreSQL.</t>
+  </si>
+  <si>
+    <t>E2E Testing (Kiểm thử toàn trình)</t>
+  </si>
+  <si>
+    <t>"Hãy viết kịch bản kiểm thử E2E bằng Cypress cho luồng: Khách hàng đặt mua nông sản -&gt; RabbitMQ xử lý -&gt; AI định tuyến -&gt; Cập nhật trạng thái."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Cung cấp mã nguồn Cypress mô phỏng thao tác click của người dùng và verify dữ liệu trả về từ Backend.
+Quyết định: Tích hợp bộ test E2E vào CI/CD pipeline để đảm bảo không vỡ luồng chính khi update code.</t>
+  </si>
+  <si>
+    <t>UAT (Kiểm thử chấp nhận người dùng)</t>
+  </si>
+  <si>
+    <t>"Xây dựng kịch bản UAT (User Acceptance Testing) tập trung vào trải nghiệm của bà con nông dân khi kiểm tra báo cáo dòng tiền trên web-app."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Tạo checklist UAT tập trung vào tính dễ hiểu của biểu đồ, độ chính xác của số dư công nợ và tốc độ tải trang.
+Quyết định: Chạy UAT với một số hợp tác xã mẫu, thu thập phản hồi và điều chỉnh lại UX/UI cho trực quan hơn.</t>
+  </si>
+  <si>
+    <t>Database Tuning (Tối ưu hóa Index)</t>
+  </si>
+  <si>
+    <t>"Bảng lịch sử giao dịch dòng tiền bắt đầu chậm khi truy vấn. Hãy hướng dẫn cách đánh Index tối ưu cho PostgreSQL."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Phân tích Execution Plan, đề xuất dùng B-Tree Index cho cột thời gian và Hash Index cho mã đơn hàng/mã nhà cung cấp.
+Quyết định: Thực thi các lệnh tạo Index, giảm thời gian load báo cáo tài chính từ 3 giây xuống dưới 500ms.</t>
+  </si>
+  <si>
+    <t>Backup Strategy (Chiến lược sao lưu)</t>
+  </si>
+  <si>
+    <t>"Cần thiết lập hệ thống tự động backup toàn bộ cơ sở dữ liệu và mã nguồn hàng ngày lên cloud để phòng rủi ro."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Cung cấp script kết hợp pg_dump và cronjob để nén dữ liệu, đẩy tự động lên AWS S3/Google Drive.
+Quyết định: Thiết lập cronjob backup lúc 2h sáng mỗi ngày, đảm bảo an toàn tuyệt đối cho dữ liệu tài chính.</t>
+  </si>
+  <si>
+    <t>User Manual (Tài liệu Hướng dẫn)</t>
+  </si>
+  <si>
+    <t>"Giúp soạn thảo dàn ý tài liệu hướng dẫn sử dụng (User Manual) thật đơn giản, dễ hiểu dành riêng cho bà con nông dân."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Lập dàn ý kèm hình ảnh minh họa từng bước: Đăng nhập, Xem doanh thu, Rút tiền, Cập nhật trạng thái kho.
+Quyết định: Xuất bản tài liệu dưới dạng PDF và Video ngắn, tích hợp sẵn vào mục Trợ giúp trên Dashboard.</t>
+  </si>
+  <si>
+    <t>Go-Live (Kiểm tra trước triển khai)</t>
+  </si>
+  <si>
+    <t>"Cung cấp Checklist các bước cuối cùng cần kiểm tra (Pre-launch Checklist) trước khi trỏ domain chính thức và mở hệ thống cho người dùng."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Gợi ý kiểm tra chứng chỉ SSL, xóa dữ liệu test, reset sequence ID trong DB, và kích hoạt môi trường Production cho mọi service.
+Quyết định: Hoàn tất checklist, dọn dẹp sạch dữ liệu rác và chính thức Go-Live hệ thống.</t>
+  </si>
+  <si>
+    <t>Monitoring (Cảnh báo hệ thống)</t>
+  </si>
+  <si>
+    <t>"Thiết lập cảnh báo tự động qua Telegram nếu hàng đợi RabbitMQ bị kẹt quá 1000 tin nhắn hoặc CPU server vượt 85%."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Hướng dẫn dùng Prometheus Alertmanager kết nối Webhook Telegram để bắn thông báo khẩn cấp.
+Quyết định: Tích hợp bot cảnh báo, giúp đội dev phản ứng tức thời nếu hệ thống quá tải trong các đợt Flash Sale.</t>
+  </si>
+  <si>
+    <t>Customer Support (Hỗ trợ trực tuyến)</t>
+  </si>
+  <si>
+    <t>"Cần tích hợp một công cụ Live Chat vào giao diện khách hàng để hỗ trợ giải đáp thắc mắc về nguồn gốc nông sản."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Đề xuất và cung cấp đoạn mã nhúng (embed script) của Tawk.to hoặc Facebook Messenger Chat Plugin.
+Quyết định: Nhúng Tawk.to vào góc phải màn hình, phân công nhân sự trực chat trong giờ hành chính.</t>
+  </si>
+  <si>
+    <t>Marketing Tracking (Theo dõi chuyển đổi)</t>
+  </si>
+  <si>
+    <t>"Hướng dẫn cài đặt Google Analytics 4 (GA4) và Facebook Pixel qua Google Tag Manager (GTM) để đo lường tỷ lệ mua hàng thành công."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Cung cấp hướng dẫn tạo Data Layer trong Next.js để bắt sự kiện purchase kèm giá trị đơn hàng đẩy về GA4.
+Quyết định: Cài đặt tracking thành công, sẵn sàng dữ liệu phục vụ các chiến dịch quảng cáo tiêu thụ nông sản.</t>
+  </si>
+  <si>
+    <t>Retrospective (Đánh giá hiệu quả)</t>
+  </si>
+  <si>
+    <t>"Dựa trên mục tiêu ban đầu là quản lý dòng tiền và tối ưu logistics, hãy phác thảo báo cáo đánh giá hiệu quả sau 1 tuần Go-Live."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Đưa ra template báo cáo gồm các chỉ số: Số giao dịch thành công, Thời gian trung bình giao hàng, Tỷ lệ lỗi hệ thống, Đánh giá từ hợp tác xã.
+Quyết định: Thu thập số liệu thực tế, lập báo cáo gửi các bên liên quan để đánh giá mức độ thành công của MVP.</t>
+  </si>
+  <si>
+    <t>Final Presentation (Bảo vệ dự án)</t>
+  </si>
+  <si>
+    <t>"Viết dàn ý chi tiết cho bài thuyết trình bảo vệ dự án, nhấn mạnh vào kiến trúc chịu tải Event-Driven và bài toán tối ưu AI."</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI: Chia dàn ý thành 15 slide: Đặt vấn đề, Giải pháp, Kiến trúc hệ thống, Thuật toán OR-Tools, Demo luồng vận hành, Hướng phát triển.
+Quyết định: Hoàn thiện Slide thuyết trình, phân công các thành viên chuẩn bị kịch bản trả lời phản biện.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -505,7 +634,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -516,23 +645,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -846,14 +981,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" customWidth="1"/>
-    <col min="4" max="4" width="72.6640625" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" customWidth="1"/>
+    <col min="4" max="4" width="72.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -867,7 +1002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -881,7 +1016,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="250.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="242.25" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -896,6 +1031,128 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A2B7EA-1CEB-4B6B-8824-1351A76B3D60}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="42.85546875" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" customWidth="1"/>
+    <col min="4" max="4" width="43.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="150" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>143</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -903,14 +1160,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" customWidth="1"/>
-    <col min="4" max="4" width="72.6640625" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" customWidth="1"/>
+    <col min="4" max="4" width="72.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -924,7 +1181,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -938,7 +1195,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -960,14 +1217,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE059D6-C78C-4518-A06A-5E141951E9CE}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.33203125" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" customWidth="1"/>
-    <col min="4" max="4" width="47.109375" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" customWidth="1"/>
+    <col min="4" max="4" width="47.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -981,7 +1238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="240" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -995,7 +1252,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="195" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1009,7 +1266,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1031,15 +1288,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5C778F-E897-444F-8693-62D09D5A0A0D}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="46.6640625" customWidth="1"/>
-    <col min="3" max="3" width="31.33203125" customWidth="1"/>
-    <col min="4" max="4" width="46.6640625" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" customWidth="1"/>
+    <col min="2" max="2" width="46.7109375" customWidth="1"/>
+    <col min="3" max="3" width="31.28515625" customWidth="1"/>
+    <col min="4" max="4" width="46.7109375" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1053,7 +1310,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="229.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="229.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1067,7 +1324,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="210" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1081,7 +1338,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="240" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1095,7 +1352,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="255" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="12" t="s">
         <v>34</v>
@@ -1115,14 +1372,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854D79C7-6BFD-4291-81B6-EE8BA46EF5FC}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="62.5546875" customWidth="1"/>
+    <col min="2" max="2" width="62.5703125" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
-    <col min="4" max="4" width="72.6640625" customWidth="1"/>
+    <col min="4" max="4" width="72.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1136,7 +1393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1150,7 +1407,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1164,7 +1421,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1178,7 +1435,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1192,7 +1449,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1206,7 +1463,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1228,14 +1485,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE75B42-A07E-44EA-A1C6-EF0F79346583}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="55.109375" customWidth="1"/>
-    <col min="3" max="3" width="37.5546875" customWidth="1"/>
-    <col min="4" max="4" width="53.33203125" customWidth="1"/>
+    <col min="2" max="2" width="55.140625" customWidth="1"/>
+    <col min="3" max="3" width="37.5703125" customWidth="1"/>
+    <col min="4" max="4" width="53.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1249,7 +1506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1263,7 +1520,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1277,7 +1534,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1291,7 +1548,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1305,7 +1562,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1319,7 +1576,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1341,15 +1598,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B94F58A-D036-43DF-B29B-7261E51DD160}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="56.109375" customWidth="1"/>
-    <col min="3" max="3" width="35.6640625" customWidth="1"/>
-    <col min="4" max="4" width="53.33203125" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" customWidth="1"/>
+    <col min="4" max="4" width="53.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1363,7 +1620,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1377,7 +1634,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1391,7 +1648,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1405,7 +1662,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1419,7 +1676,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1433,7 +1690,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1455,14 +1712,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F7923E-0FE5-4029-9481-11345A93CD30}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="51.33203125" customWidth="1"/>
-    <col min="3" max="3" width="32.88671875" customWidth="1"/>
+    <col min="2" max="2" width="51.28515625" customWidth="1"/>
+    <col min="3" max="3" width="32.85546875" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1476,7 +1733,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="180" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1490,7 +1747,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1504,7 +1761,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1518,7 +1775,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1532,7 +1789,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="165" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1546,7 +1803,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="150" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1566,10 +1823,115 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BDEA450-7DE7-4544-BD86-947DA1712CB8}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.7109375" customWidth="1"/>
+    <col min="2" max="2" width="47.5703125" customWidth="1"/>
+    <col min="3" max="3" width="46.42578125" customWidth="1"/>
+    <col min="4" max="4" width="47.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>